--- a/ip_data/nostr/ground_truth/ground_truth.xlsx
+++ b/ip_data/nostr/ground_truth/ground_truth.xlsx
@@ -14,80 +14,85 @@
     <ns0:row r="1">
       <ns0:c r="A1" t="inlineStr">
         <ns0:is>
-          <ns0:t>ip</ns0:t>
+          <ns0:t>ip_source</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B1" t="inlineStr">
         <ns0:is>
+          <ns0:t>ip_id</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C1" t="inlineStr">
+        <ns0:is>
           <ns0:t>reviewer</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="C1" t="inlineStr">
+      <ns0:c r="D1" t="inlineStr">
         <ns0:is>
           <ns0:t>reviewed_at</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="D1" t="inlineStr">
+      <ns0:c r="E1" t="inlineStr">
         <ns0:is>
           <ns0:t>sampling_strategy</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="E1" t="inlineStr">
+      <ns0:c r="F1" t="inlineStr">
         <ns0:is>
           <ns0:t>sampling_snapshot</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="F1" t="inlineStr">
+      <ns0:c r="G1" t="inlineStr">
         <ns0:is>
           <ns0:t>sampling_seed</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="G1" t="inlineStr">
+      <ns0:c r="H1" t="inlineStr">
         <ns0:is>
           <ns0:t>era_bucket</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="H1" t="inlineStr">
+      <ns0:c r="I1" t="inlineStr">
         <ns0:is>
           <ns0:t>density_bucket</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="I1" t="inlineStr">
+      <ns0:c r="J1" t="inlineStr">
         <ns0:is>
           <ns0:t>density_basis</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="J1" t="inlineStr">
+      <ns0:c r="K1" t="inlineStr">
         <ns0:is>
           <ns0:t>created</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="K1" t="inlineStr">
+      <ns0:c r="L1" t="inlineStr">
         <ns0:is>
           <ns0:t>status</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="L1" t="inlineStr">
+      <ns0:c r="M1" t="inlineStr">
         <ns0:is>
           <ns0:t>type</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="M1" t="inlineStr">
+      <ns0:c r="N1" t="inlineStr">
         <ns0:is>
           <ns0:t>layer</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N1" t="inlineStr">
+      <ns0:c r="O1" t="inlineStr">
         <ns0:is>
           <ns0:t>title</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="O1" t="inlineStr">
+      <ns0:c r="P1" t="inlineStr">
         <ns0:is>
           <ns0:t>extracted_target_count</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="P1" t="inlineStr">
+      <ns0:c r="Q1" t="inlineStr">
         <ns0:is>
           <ns0:t>note</ns0:t>
         </ns0:is>
@@ -96,65 +101,70 @@
     <ns0:row r="2">
       <ns0:c r="A2" t="inlineStr">
         <ns0:is>
-          <ns0:t>nips:02</ns0:t>
+          <ns0:t>nips</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B2" t="inlineStr">
         <ns0:is>
-          <ns0:t>rbo</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="D2" t="inlineStr">
+          <ns0:t>02</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>rbo</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E2" t="inlineStr">
         <ns0:is>
           <ns0:t>sampler</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="E2" t="inlineStr">
+      <ns0:c r="F2" t="inlineStr">
         <ns0:is>
           <ns0:t>2026-05-30</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="F2" t="inlineStr">
+      <ns0:c r="G2" t="inlineStr">
         <ns0:is>
           <ns0:t>42</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="G2" t="inlineStr">
+      <ns0:c r="H2" t="inlineStr">
         <ns0:is>
           <ns0:t>early</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="H2" t="inlineStr">
+      <ns0:c r="I2" t="inlineStr">
         <ns0:is>
           <ns0:t>none</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="I2" t="inlineStr">
+      <ns0:c r="J2" t="inlineStr">
         <ns0:is>
           <ns0:t>llm_only</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="J2" t="inlineStr">
+      <ns0:c r="K2" t="inlineStr">
         <ns0:is>
           <ns0:t>2022-05-01</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="K2" t="inlineStr">
+      <ns0:c r="L2" t="inlineStr">
         <ns0:is>
           <ns0:t>Final</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="L2" t="inlineStr">
+      <ns0:c r="M2" t="inlineStr">
         <ns0:is>
           <ns0:t>Optional</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N2" t="inlineStr">
+      <ns0:c r="O2" t="inlineStr">
         <ns0:is>
           <ns0:t>Follow List</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="O2" t="inlineStr">
+      <ns0:c r="P2" t="inlineStr">
         <ns0:is>
           <ns0:t>0</ns0:t>
         </ns0:is>
@@ -163,75 +173,80 @@
     <ns0:row r="3">
       <ns0:c r="A3" t="inlineStr">
         <ns0:is>
-          <ns0:t>nips:17</ns0:t>
+          <ns0:t>nips</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B3" t="inlineStr">
         <ns0:is>
-          <ns0:t>rbo</ns0:t>
+          <ns0:t>17</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C3" t="inlineStr">
         <ns0:is>
+          <ns0:t>rbo</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D3" t="inlineStr">
+        <ns0:is>
           <ns0:t>2026-06-22</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="D3" t="inlineStr">
+      <ns0:c r="E3" t="inlineStr">
         <ns0:is>
           <ns0:t>manual</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="E3" t="inlineStr">
+      <ns0:c r="F3" t="inlineStr">
         <ns0:is>
           <ns0:t>-</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="F3" t="inlineStr">
+      <ns0:c r="G3" t="inlineStr">
         <ns0:is>
           <ns0:t>-</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="G3" t="inlineStr">
+      <ns0:c r="H3" t="inlineStr">
         <ns0:is>
           <ns0:t>-</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="H3" t="inlineStr">
+      <ns0:c r="I3" t="inlineStr">
         <ns0:is>
           <ns0:t>-</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="I3" t="inlineStr">
+      <ns0:c r="J3" t="inlineStr">
         <ns0:is>
           <ns0:t>-</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="J3" t="inlineStr">
+      <ns0:c r="K3" t="inlineStr">
         <ns0:is>
           <ns0:t>2023-08-09</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="K3" t="inlineStr">
+      <ns0:c r="L3" t="inlineStr">
         <ns0:is>
           <ns0:t>Draft</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="L3" t="inlineStr">
+      <ns0:c r="M3" t="inlineStr">
         <ns0:is>
           <ns0:t>Optional</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="M3" t="inlineStr">
+      <ns0:c r="N3" t="inlineStr">
         <ns0:is>
           <ns0:t>Relay</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N3" t="inlineStr">
+      <ns0:c r="O3" t="inlineStr">
         <ns0:is>
           <ns0:t>Private Direct Messages</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="O3" t="inlineStr">
+      <ns0:c r="P3" t="inlineStr">
         <ns0:is>
           <ns0:t>5</ns0:t>
         </ns0:is>
@@ -240,65 +255,70 @@
     <ns0:row r="4">
       <ns0:c r="A4" t="inlineStr">
         <ns0:is>
-          <ns0:t>nips:22</ns0:t>
+          <ns0:t>nips</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B4" t="inlineStr">
         <ns0:is>
-          <ns0:t>rbo</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="D4" t="inlineStr">
+          <ns0:t>22</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C4" t="inlineStr">
+        <ns0:is>
+          <ns0:t>rbo</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E4" t="inlineStr">
         <ns0:is>
           <ns0:t>sampler</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="E4" t="inlineStr">
+      <ns0:c r="F4" t="inlineStr">
         <ns0:is>
           <ns0:t>2026-05-30</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="F4" t="inlineStr">
+      <ns0:c r="G4" t="inlineStr">
         <ns0:is>
           <ns0:t>42</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="G4" t="inlineStr">
+      <ns0:c r="H4" t="inlineStr">
         <ns0:is>
           <ns0:t>early</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="H4" t="inlineStr">
+      <ns0:c r="I4" t="inlineStr">
         <ns0:is>
           <ns0:t>high</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="I4" t="inlineStr">
+      <ns0:c r="J4" t="inlineStr">
         <ns0:is>
           <ns0:t>llm_only</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="J4" t="inlineStr">
+      <ns0:c r="K4" t="inlineStr">
         <ns0:is>
           <ns0:t>2022-07-22</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="K4" t="inlineStr">
+      <ns0:c r="L4" t="inlineStr">
         <ns0:is>
           <ns0:t>Draft</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="L4" t="inlineStr">
+      <ns0:c r="M4" t="inlineStr">
         <ns0:is>
           <ns0:t>Optional</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N4" t="inlineStr">
+      <ns0:c r="O4" t="inlineStr">
         <ns0:is>
           <ns0:t>Comment</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="O4" t="inlineStr">
+      <ns0:c r="P4" t="inlineStr">
         <ns0:is>
           <ns0:t>4</ns0:t>
         </ns0:is>
@@ -307,65 +327,70 @@
     <ns0:row r="5">
       <ns0:c r="A5" t="inlineStr">
         <ns0:is>
-          <ns0:t>nips:27</ns0:t>
+          <ns0:t>nips</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B5" t="inlineStr">
         <ns0:is>
-          <ns0:t>rbo</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="D5" t="inlineStr">
+          <ns0:t>27</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C5" t="inlineStr">
+        <ns0:is>
+          <ns0:t>rbo</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E5" t="inlineStr">
         <ns0:is>
           <ns0:t>sampler</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="E5" t="inlineStr">
+      <ns0:c r="F5" t="inlineStr">
         <ns0:is>
           <ns0:t>2026-05-30</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="F5" t="inlineStr">
+      <ns0:c r="G5" t="inlineStr">
         <ns0:is>
           <ns0:t>42</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="G5" t="inlineStr">
+      <ns0:c r="H5" t="inlineStr">
         <ns0:is>
           <ns0:t>early</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="H5" t="inlineStr">
+      <ns0:c r="I5" t="inlineStr">
         <ns0:is>
           <ns0:t>high</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="I5" t="inlineStr">
+      <ns0:c r="J5" t="inlineStr">
         <ns0:is>
           <ns0:t>llm_only</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="J5" t="inlineStr">
+      <ns0:c r="K5" t="inlineStr">
         <ns0:is>
           <ns0:t>2022-08-16</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="K5" t="inlineStr">
+      <ns0:c r="L5" t="inlineStr">
         <ns0:is>
           <ns0:t>Draft</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="L5" t="inlineStr">
+      <ns0:c r="M5" t="inlineStr">
         <ns0:is>
           <ns0:t>Optional</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N5" t="inlineStr">
+      <ns0:c r="O5" t="inlineStr">
         <ns0:is>
           <ns0:t>Text Note References</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="O5" t="inlineStr">
+      <ns0:c r="P5" t="inlineStr">
         <ns0:is>
           <ns0:t>4</ns0:t>
         </ns0:is>
@@ -374,65 +399,70 @@
     <ns0:row r="6">
       <ns0:c r="A6" t="inlineStr">
         <ns0:is>
-          <ns0:t>nips:28</ns0:t>
+          <ns0:t>nips</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B6" t="inlineStr">
         <ns0:is>
-          <ns0:t>rbo</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="D6" t="inlineStr">
+          <ns0:t>28</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C6" t="inlineStr">
+        <ns0:is>
+          <ns0:t>rbo</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E6" t="inlineStr">
         <ns0:is>
           <ns0:t>sampler</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="E6" t="inlineStr">
+      <ns0:c r="F6" t="inlineStr">
         <ns0:is>
           <ns0:t>2026-05-30</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="F6" t="inlineStr">
+      <ns0:c r="G6" t="inlineStr">
         <ns0:is>
           <ns0:t>42</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="G6" t="inlineStr">
+      <ns0:c r="H6" t="inlineStr">
         <ns0:is>
           <ns0:t>early</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="H6" t="inlineStr">
+      <ns0:c r="I6" t="inlineStr">
         <ns0:is>
           <ns0:t>low</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="I6" t="inlineStr">
+      <ns0:c r="J6" t="inlineStr">
         <ns0:is>
           <ns0:t>llm_only</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="J6" t="inlineStr">
+      <ns0:c r="K6" t="inlineStr">
         <ns0:is>
           <ns0:t>2022-09-10</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="K6" t="inlineStr">
+      <ns0:c r="L6" t="inlineStr">
         <ns0:is>
           <ns0:t>Draft</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="L6" t="inlineStr">
+      <ns0:c r="M6" t="inlineStr">
         <ns0:is>
           <ns0:t>Optional</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N6" t="inlineStr">
+      <ns0:c r="O6" t="inlineStr">
         <ns0:is>
           <ns0:t>Public Chat</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="O6" t="inlineStr">
+      <ns0:c r="P6" t="inlineStr">
         <ns0:is>
           <ns0:t>1</ns0:t>
         </ns0:is>
@@ -441,65 +471,70 @@
     <ns0:row r="7">
       <ns0:c r="A7" t="inlineStr">
         <ns0:is>
-          <ns0:t>nips:34</ns0:t>
+          <ns0:t>nips</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B7" t="inlineStr">
         <ns0:is>
-          <ns0:t>rbo</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="D7" t="inlineStr">
+          <ns0:t>34</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C7" t="inlineStr">
+        <ns0:is>
+          <ns0:t>rbo</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E7" t="inlineStr">
         <ns0:is>
           <ns0:t>sampler</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="E7" t="inlineStr">
+      <ns0:c r="F7" t="inlineStr">
         <ns0:is>
           <ns0:t>2026-05-30</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="F7" t="inlineStr">
+      <ns0:c r="G7" t="inlineStr">
         <ns0:is>
           <ns0:t>42</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="G7" t="inlineStr">
+      <ns0:c r="H7" t="inlineStr">
         <ns0:is>
           <ns0:t>recent</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="H7" t="inlineStr">
+      <ns0:c r="I7" t="inlineStr">
         <ns0:is>
           <ns0:t>high</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="I7" t="inlineStr">
+      <ns0:c r="J7" t="inlineStr">
         <ns0:is>
           <ns0:t>llm_only</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="J7" t="inlineStr">
+      <ns0:c r="K7" t="inlineStr">
         <ns0:is>
           <ns0:t>2024-03-05</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="K7" t="inlineStr">
+      <ns0:c r="L7" t="inlineStr">
         <ns0:is>
           <ns0:t>Draft</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="L7" t="inlineStr">
+      <ns0:c r="M7" t="inlineStr">
         <ns0:is>
           <ns0:t>Optional</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N7" t="inlineStr">
+      <ns0:c r="O7" t="inlineStr">
         <ns0:is>
           <ns0:t>`git` stuff</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="O7" t="inlineStr">
+      <ns0:c r="P7" t="inlineStr">
         <ns0:is>
           <ns0:t>3</ns0:t>
         </ns0:is>
@@ -508,65 +543,70 @@
     <ns0:row r="8">
       <ns0:c r="A8" t="inlineStr">
         <ns0:is>
-          <ns0:t>nips:56</ns0:t>
+          <ns0:t>nips</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B8" t="inlineStr">
         <ns0:is>
-          <ns0:t>rbo</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="D8" t="inlineStr">
+          <ns0:t>56</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C8" t="inlineStr">
+        <ns0:is>
+          <ns0:t>rbo</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E8" t="inlineStr">
         <ns0:is>
           <ns0:t>sampler</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="E8" t="inlineStr">
+      <ns0:c r="F8" t="inlineStr">
         <ns0:is>
           <ns0:t>2026-05-30</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="F8" t="inlineStr">
+      <ns0:c r="G8" t="inlineStr">
         <ns0:is>
           <ns0:t>42</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="G8" t="inlineStr">
+      <ns0:c r="H8" t="inlineStr">
         <ns0:is>
           <ns0:t>middle</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="H8" t="inlineStr">
+      <ns0:c r="I8" t="inlineStr">
         <ns0:is>
           <ns0:t>low</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="I8" t="inlineStr">
+      <ns0:c r="J8" t="inlineStr">
         <ns0:is>
           <ns0:t>llm_only</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="J8" t="inlineStr">
+      <ns0:c r="K8" t="inlineStr">
         <ns0:is>
           <ns0:t>2023-02-07</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="K8" t="inlineStr">
+      <ns0:c r="L8" t="inlineStr">
         <ns0:is>
           <ns0:t>Unknown</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="L8" t="inlineStr">
+      <ns0:c r="M8" t="inlineStr">
         <ns0:is>
           <ns0:t>Optional</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N8" t="inlineStr">
+      <ns0:c r="O8" t="inlineStr">
         <ns0:is>
           <ns0:t>Reporting</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="O8" t="inlineStr">
+      <ns0:c r="P8" t="inlineStr">
         <ns0:is>
           <ns0:t>1</ns0:t>
         </ns0:is>
@@ -575,65 +615,70 @@
     <ns0:row r="9">
       <ns0:c r="A9" t="inlineStr">
         <ns0:is>
-          <ns0:t>nips:73</ns0:t>
+          <ns0:t>nips</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B9" t="inlineStr">
         <ns0:is>
-          <ns0:t>rbo</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="D9" t="inlineStr">
+          <ns0:t>73</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C9" t="inlineStr">
+        <ns0:is>
+          <ns0:t>rbo</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E9" t="inlineStr">
         <ns0:is>
           <ns0:t>sampler</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="E9" t="inlineStr">
+      <ns0:c r="F9" t="inlineStr">
         <ns0:is>
           <ns0:t>2026-05-30</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="F9" t="inlineStr">
+      <ns0:c r="G9" t="inlineStr">
         <ns0:is>
           <ns0:t>42</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="G9" t="inlineStr">
+      <ns0:c r="H9" t="inlineStr">
         <ns0:is>
           <ns0:t>recent</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="H9" t="inlineStr">
+      <ns0:c r="I9" t="inlineStr">
         <ns0:is>
           <ns0:t>none</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="I9" t="inlineStr">
+      <ns0:c r="J9" t="inlineStr">
         <ns0:is>
           <ns0:t>llm_only</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="J9" t="inlineStr">
+      <ns0:c r="K9" t="inlineStr">
         <ns0:is>
           <ns0:t>2024-08-05</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="K9" t="inlineStr">
+      <ns0:c r="L9" t="inlineStr">
         <ns0:is>
           <ns0:t>Draft</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="L9" t="inlineStr">
+      <ns0:c r="M9" t="inlineStr">
         <ns0:is>
           <ns0:t>Optional</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N9" t="inlineStr">
+      <ns0:c r="O9" t="inlineStr">
         <ns0:is>
           <ns0:t>External Content IDs</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="O9" t="inlineStr">
+      <ns0:c r="P9" t="inlineStr">
         <ns0:is>
           <ns0:t>0</ns0:t>
         </ns0:is>
@@ -642,65 +687,70 @@
     <ns0:row r="10">
       <ns0:c r="A10" t="inlineStr">
         <ns0:is>
-          <ns0:t>nips:89</ns0:t>
+          <ns0:t>nips</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B10" t="inlineStr">
         <ns0:is>
-          <ns0:t>rbo</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="D10" t="inlineStr">
+          <ns0:t>89</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C10" t="inlineStr">
+        <ns0:is>
+          <ns0:t>rbo</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E10" t="inlineStr">
         <ns0:is>
           <ns0:t>sampler</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="E10" t="inlineStr">
+      <ns0:c r="F10" t="inlineStr">
         <ns0:is>
           <ns0:t>2026-05-30</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="F10" t="inlineStr">
+      <ns0:c r="G10" t="inlineStr">
         <ns0:is>
           <ns0:t>42</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="G10" t="inlineStr">
+      <ns0:c r="H10" t="inlineStr">
         <ns0:is>
           <ns0:t>middle</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="H10" t="inlineStr">
+      <ns0:c r="I10" t="inlineStr">
         <ns0:is>
           <ns0:t>high</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="I10" t="inlineStr">
+      <ns0:c r="J10" t="inlineStr">
         <ns0:is>
           <ns0:t>llm_only</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="J10" t="inlineStr">
+      <ns0:c r="K10" t="inlineStr">
         <ns0:is>
           <ns0:t>2023-06-07</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="K10" t="inlineStr">
+      <ns0:c r="L10" t="inlineStr">
         <ns0:is>
           <ns0:t>Draft</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="L10" t="inlineStr">
+      <ns0:c r="M10" t="inlineStr">
         <ns0:is>
           <ns0:t>Optional</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N10" t="inlineStr">
+      <ns0:c r="O10" t="inlineStr">
         <ns0:is>
           <ns0:t>Recommended Application Handlers</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="O10" t="inlineStr">
+      <ns0:c r="P10" t="inlineStr">
         <ns0:is>
           <ns0:t>3</ns0:t>
         </ns0:is>
@@ -709,65 +759,70 @@
     <ns0:row r="11">
       <ns0:c r="A11" t="inlineStr">
         <ns0:is>
-          <ns0:t>nips:98</ns0:t>
+          <ns0:t>nips</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B11" t="inlineStr">
         <ns0:is>
-          <ns0:t>rbo</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="D11" t="inlineStr">
+          <ns0:t>98</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C11" t="inlineStr">
+        <ns0:is>
+          <ns0:t>rbo</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E11" t="inlineStr">
         <ns0:is>
           <ns0:t>sampler</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="E11" t="inlineStr">
+      <ns0:c r="F11" t="inlineStr">
         <ns0:is>
           <ns0:t>2026-05-30</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="F11" t="inlineStr">
+      <ns0:c r="G11" t="inlineStr">
         <ns0:is>
           <ns0:t>42</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="G11" t="inlineStr">
+      <ns0:c r="H11" t="inlineStr">
         <ns0:is>
           <ns0:t>middle</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="H11" t="inlineStr">
+      <ns0:c r="I11" t="inlineStr">
         <ns0:is>
           <ns0:t>none</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="I11" t="inlineStr">
+      <ns0:c r="J11" t="inlineStr">
         <ns0:is>
           <ns0:t>llm_only</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="J11" t="inlineStr">
+      <ns0:c r="K11" t="inlineStr">
         <ns0:is>
           <ns0:t>2023-04-24</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="K11" t="inlineStr">
+      <ns0:c r="L11" t="inlineStr">
         <ns0:is>
           <ns0:t>Draft</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="L11" t="inlineStr">
+      <ns0:c r="M11" t="inlineStr">
         <ns0:is>
           <ns0:t>Optional</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N11" t="inlineStr">
+      <ns0:c r="O11" t="inlineStr">
         <ns0:is>
           <ns0:t>HTTP Auth</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="O11" t="inlineStr">
+      <ns0:c r="P11" t="inlineStr">
         <ns0:is>
           <ns0:t>0</ns0:t>
         </ns0:is>
@@ -776,60 +831,65 @@
     <ns0:row r="12">
       <ns0:c r="A12" t="inlineStr">
         <ns0:is>
-          <ns0:t>nips:A0</ns0:t>
+          <ns0:t>nips</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B12" t="inlineStr">
         <ns0:is>
-          <ns0:t>rbo</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="D12" t="inlineStr">
+          <ns0:t>A0</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>rbo</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E12" t="inlineStr">
         <ns0:is>
           <ns0:t>sampler</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="E12" t="inlineStr">
+      <ns0:c r="F12" t="inlineStr">
         <ns0:is>
           <ns0:t>2026-05-30</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="F12" t="inlineStr">
+      <ns0:c r="G12" t="inlineStr">
         <ns0:is>
           <ns0:t>42</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="G12" t="inlineStr">
+      <ns0:c r="H12" t="inlineStr">
         <ns0:is>
           <ns0:t>recent</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="H12" t="inlineStr">
+      <ns0:c r="I12" t="inlineStr">
         <ns0:is>
           <ns0:t>low</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="I12" t="inlineStr">
+      <ns0:c r="J12" t="inlineStr">
         <ns0:is>
           <ns0:t>llm_only</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="J12" t="inlineStr">
+      <ns0:c r="K12" t="inlineStr">
         <ns0:is>
           <ns0:t>2025-07-23</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="K12" t="inlineStr">
+      <ns0:c r="L12" t="inlineStr">
         <ns0:is>
           <ns0:t>Draft</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N12" t="inlineStr">
+      <ns0:c r="O12" t="inlineStr">
         <ns0:is>
           <ns0:t>Voice Messages</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="O12" t="inlineStr">
+      <ns0:c r="P12" t="inlineStr">
         <ns0:is>
           <ns0:t>2</ns0:t>
         </ns0:is>
@@ -850,35 +910,45 @@
       </ns0:c>
       <ns0:c r="B1" t="inlineStr">
         <ns0:is>
+          <ns0:t>source_id</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C1" t="inlineStr">
+        <ns0:is>
           <ns0:t>target</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="C1" t="inlineStr">
+      <ns0:c r="D1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>target_id</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E1" t="inlineStr">
         <ns0:is>
           <ns0:t>relation_type</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="D1" t="inlineStr">
+      <ns0:c r="F1" t="inlineStr">
         <ns0:is>
           <ns0:t>confidence</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="E1" t="inlineStr">
+      <ns0:c r="G1" t="inlineStr">
         <ns0:is>
           <ns0:t>evidence</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="F1" t="inlineStr">
+      <ns0:c r="H1" t="inlineStr">
         <ns0:is>
           <ns0:t>note</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="G1" t="inlineStr">
+      <ns0:c r="I1" t="inlineStr">
         <ns0:is>
           <ns0:t>reviewer</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="H1" t="inlineStr">
+      <ns0:c r="J1" t="inlineStr">
         <ns0:is>
           <ns0:t>reviewed_at</ns0:t>
         </ns0:is>
@@ -887,35 +957,45 @@
     <ns0:row r="2">
       <ns0:c r="A2" t="inlineStr">
         <ns0:is>
-          <ns0:t>nips:17</ns0:t>
+          <ns0:t>nips</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B2" t="inlineStr">
         <ns0:is>
-          <ns0:t>nips:44</ns0:t>
+          <ns0:t>17</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C2" t="inlineStr">
         <ns0:is>
+          <ns0:t>nips</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>44</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E2" t="inlineStr">
+        <ns0:is>
           <ns0:t>depends_on</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="D2" t="inlineStr">
+      <ns0:c r="F2" t="inlineStr">
         <ns0:is>
           <ns0:t>high</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="E2" t="inlineStr">
+      <ns0:c r="G2" t="inlineStr">
         <ns0:is>
           <ns0:t>This NIP defines an encrypted chat scheme which uses NIP-44 encryption</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="G2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>rbo</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="H2" t="inlineStr">
+      <ns0:c r="I2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>rbo</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J2" t="inlineStr">
         <ns0:is>
           <ns0:t>2026-06-22</ns0:t>
         </ns0:is>
@@ -924,35 +1004,45 @@
     <ns0:row r="3">
       <ns0:c r="A3" t="inlineStr">
         <ns0:is>
-          <ns0:t>nips:17</ns0:t>
+          <ns0:t>nips</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B3" t="inlineStr">
         <ns0:is>
-          <ns0:t>nips:59</ns0:t>
+          <ns0:t>17</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C3" t="inlineStr">
         <ns0:is>
+          <ns0:t>nips</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>59</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E3" t="inlineStr">
+        <ns0:is>
           <ns0:t>depends_on</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="D3" t="inlineStr">
+      <ns0:c r="F3" t="inlineStr">
         <ns0:is>
           <ns0:t>high</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="E3" t="inlineStr">
+      <ns0:c r="G3" t="inlineStr">
         <ns0:is>
           <ns0:t>This NIP defines an encrypted chat scheme which uses [...] NIP-59 gift-wrapping. [...] Following NIP-59, the unsigned chat messages must be sealed (kind:13) and then gift-wrapped (kind:1059)</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="G3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>rbo</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="H3" t="inlineStr">
+      <ns0:c r="I3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>rbo</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J3" t="inlineStr">
         <ns0:is>
           <ns0:t>2026-06-22</ns0:t>
         </ns0:is>
